--- a/shortlist látek.xlsx
+++ b/shortlist látek.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paxin45\Documents\Škola\Vysoká\Energetika\2.semestr\PRO2\model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED48217E-CC6C-4697-8EE8-F796CEA11649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD742C3-99D3-4EF0-9014-FF4D594E9FDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2637,7 +2637,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2669,13 +2669,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2690,58 +2690,11 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="41">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="27"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border outline="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
+  <dxfs count="35">
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -2761,44 +2714,6 @@
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF99CCFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2911,6 +2826,47 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="27"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
       <border outline="0">
         <left style="medium">
           <color indexed="64"/>
@@ -2924,64 +2880,42 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF99CCFF"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2997,42 +2931,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8952ADBB-AB0A-4B29-A11C-38382C544CF0}" name="Tabulka1" displayName="Tabulka1" ref="A1:AD91" totalsRowShown="0" headerRowDxfId="4" dataDxfId="5" tableBorderDxfId="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8952ADBB-AB0A-4B29-A11C-38382C544CF0}" name="Tabulka1" displayName="Tabulka1" ref="A1:AD91" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33" tableBorderDxfId="32">
   <autoFilter ref="A1:AD91" xr:uid="{8952ADBB-AB0A-4B29-A11C-38382C544CF0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD91">
     <sortCondition ref="A1:A91"/>
   </sortState>
   <tableColumns count="30">
-    <tableColumn id="1" xr3:uid="{4859F279-FC01-4C27-A1A5-963515418110}" name="Short name" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{9D918637-9E7E-4010-AA02-208CB900E369}" name="New in Version 10" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{8AE6DCBC-45CE-48FA-AD49-C19F4848CE06}" name="Full name" dataDxfId="33"/>
-    <tableColumn id="4" xr3:uid="{ED7173EC-443D-45C3-8486-04B63BCEA025}" name="Synonym" dataDxfId="32"/>
-    <tableColumn id="5" xr3:uid="{89218849-C153-447C-BB8C-9529DCE61A2B}" name="Fluid file" dataDxfId="31"/>
-    <tableColumn id="6" xr3:uid="{652E5239-C1CD-4F73-9EDF-200F153B00E2}" name="Chemical Formula" dataDxfId="30"/>
-    <tableColumn id="7" xr3:uid="{D57673D5-9493-4CD5-8E4D-F6A42B330345}" name="Short Formula" dataDxfId="29"/>
-    <tableColumn id="8" xr3:uid="{50B3EFE6-C314-4E9E-BFBB-6B2D5C89FCCD}" name="Molar Mass (g/mol)" dataDxfId="28"/>
-    <tableColumn id="9" xr3:uid="{97A55931-6C93-46E0-9A66-77F0AC19B2C3}" name="Boiling point temperature (K)" dataDxfId="27"/>
-    <tableColumn id="10" xr3:uid="{0D48F59E-5805-4BD7-90B8-BB203D213032}" name="Triple point temperature (K)" dataDxfId="26"/>
-    <tableColumn id="11" xr3:uid="{8A3C87BB-D096-4880-9DDF-DE106CE38FEC}" name="Critical temperature (K)" dataDxfId="25"/>
-    <tableColumn id="12" xr3:uid="{E3F0D311-7974-422B-9340-F384B244EC97}" name="Critical pressure (MPa)" dataDxfId="24"/>
-    <tableColumn id="13" xr3:uid="{89A46A5B-ADF7-4137-AD04-440259E37209}" name="Critical density (mol/dm^3)" dataDxfId="23"/>
-    <tableColumn id="14" xr3:uid="{68C131BF-3403-4DE1-AAD6-A7B82E508BFE}" name="Dipole moment" dataDxfId="22"/>
-    <tableColumn id="15" xr3:uid="{4D47F5A5-848F-4A11-8B88-106280F84F37}" name="Acentric factor" dataDxfId="21"/>
-    <tableColumn id="16" xr3:uid="{07CBCDAE-CA14-48C8-BBBB-F0C6854F6FC8}" name="Heating value (J/mol)" dataDxfId="20"/>
-    <tableColumn id="17" xr3:uid="{F972A04D-4EAF-425A-B9E5-091DD624EBA1}" name="Heat of Formation (J/mol)" dataDxfId="19"/>
-    <tableColumn id="18" xr3:uid="{D1325E70-8378-4AB2-86F2-8FC5D687B82B}" name="Family" dataDxfId="18"/>
-    <tableColumn id="19" xr3:uid="{8DCA0511-38EB-4BF6-86CA-D53AC0875624}" name="Lower temperature limit (K)" dataDxfId="17"/>
-    <tableColumn id="20" xr3:uid="{EFC6156D-EF61-4EA6-80BF-B1F280DA1B59}" name="Upper temperature limit (K)" dataDxfId="16"/>
-    <tableColumn id="21" xr3:uid="{233E8B9E-CD50-4B55-89A3-F32DA6D591FC}" name="Upper pressure limit (MPa)" dataDxfId="15"/>
-    <tableColumn id="22" xr3:uid="{0895640E-8685-4B0F-BA79-3CB1D2D2B02D}" name="CAS number" dataDxfId="14"/>
-    <tableColumn id="23" xr3:uid="{C0092A17-DCF1-4467-98F1-2B13661648B7}" name="Hash" dataDxfId="13"/>
-    <tableColumn id="24" xr3:uid="{38B36995-8E7A-49D3-9503-D0A1019F317A}" name="Reference state" dataDxfId="12"/>
-    <tableColumn id="25" xr3:uid="{17FC834C-7B96-49A9-A82F-9343E27C57D0}" name="UN number" dataDxfId="11"/>
-    <tableColumn id="26" xr3:uid="{F6716D83-DE4C-4DCE-959E-D483CF0FB8CE}" name="GWP" dataDxfId="10"/>
-    <tableColumn id="27" xr3:uid="{7265A8D0-CFF6-415F-835D-AB8059EE6183}" name="ODP" dataDxfId="9"/>
-    <tableColumn id="28" xr3:uid="{3BF8A3E1-4D9A-459C-B9C8-5CD0C527F418}" name="ASHRAE 34 Safety Classification" dataDxfId="8"/>
-    <tableColumn id="29" xr3:uid="{27A813A0-C128-44A4-AA80-8DA82CC43079}" name="Standard InChI Key" dataDxfId="7"/>
-    <tableColumn id="30" xr3:uid="{CA650C7B-A0BE-4110-8763-174A6A5C98DF}" name="Standard InChI String" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{4859F279-FC01-4C27-A1A5-963515418110}" name="Short name" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{9D918637-9E7E-4010-AA02-208CB900E369}" name="New in Version 10" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{8AE6DCBC-45CE-48FA-AD49-C19F4848CE06}" name="Full name" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{ED7173EC-443D-45C3-8486-04B63BCEA025}" name="Synonym" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{89218849-C153-447C-BB8C-9529DCE61A2B}" name="Fluid file" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{652E5239-C1CD-4F73-9EDF-200F153B00E2}" name="Chemical Formula" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{D57673D5-9493-4CD5-8E4D-F6A42B330345}" name="Short Formula" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{50B3EFE6-C314-4E9E-BFBB-6B2D5C89FCCD}" name="Molar Mass (g/mol)" dataDxfId="24"/>
+    <tableColumn id="9" xr3:uid="{97A55931-6C93-46E0-9A66-77F0AC19B2C3}" name="Boiling point temperature (K)" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{0D48F59E-5805-4BD7-90B8-BB203D213032}" name="Triple point temperature (K)" dataDxfId="22"/>
+    <tableColumn id="11" xr3:uid="{8A3C87BB-D096-4880-9DDF-DE106CE38FEC}" name="Critical temperature (K)" dataDxfId="21"/>
+    <tableColumn id="12" xr3:uid="{E3F0D311-7974-422B-9340-F384B244EC97}" name="Critical pressure (MPa)" dataDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{89A46A5B-ADF7-4137-AD04-440259E37209}" name="Critical density (mol/dm^3)" dataDxfId="19"/>
+    <tableColumn id="14" xr3:uid="{68C131BF-3403-4DE1-AAD6-A7B82E508BFE}" name="Dipole moment" dataDxfId="18"/>
+    <tableColumn id="15" xr3:uid="{4D47F5A5-848F-4A11-8B88-106280F84F37}" name="Acentric factor" dataDxfId="17"/>
+    <tableColumn id="16" xr3:uid="{07CBCDAE-CA14-48C8-BBBB-F0C6854F6FC8}" name="Heating value (J/mol)" dataDxfId="16"/>
+    <tableColumn id="17" xr3:uid="{F972A04D-4EAF-425A-B9E5-091DD624EBA1}" name="Heat of Formation (J/mol)" dataDxfId="15"/>
+    <tableColumn id="18" xr3:uid="{D1325E70-8378-4AB2-86F2-8FC5D687B82B}" name="Family" dataDxfId="14"/>
+    <tableColumn id="19" xr3:uid="{8DCA0511-38EB-4BF6-86CA-D53AC0875624}" name="Lower temperature limit (K)" dataDxfId="13"/>
+    <tableColumn id="20" xr3:uid="{EFC6156D-EF61-4EA6-80BF-B1F280DA1B59}" name="Upper temperature limit (K)" dataDxfId="12"/>
+    <tableColumn id="21" xr3:uid="{233E8B9E-CD50-4B55-89A3-F32DA6D591FC}" name="Upper pressure limit (MPa)" dataDxfId="11"/>
+    <tableColumn id="22" xr3:uid="{0895640E-8685-4B0F-BA79-3CB1D2D2B02D}" name="CAS number" dataDxfId="10"/>
+    <tableColumn id="23" xr3:uid="{C0092A17-DCF1-4467-98F1-2B13661648B7}" name="Hash" dataDxfId="9"/>
+    <tableColumn id="24" xr3:uid="{38B36995-8E7A-49D3-9503-D0A1019F317A}" name="Reference state" dataDxfId="8"/>
+    <tableColumn id="25" xr3:uid="{17FC834C-7B96-49A9-A82F-9343E27C57D0}" name="UN number" dataDxfId="7"/>
+    <tableColumn id="26" xr3:uid="{F6716D83-DE4C-4DCE-959E-D483CF0FB8CE}" name="GWP" dataDxfId="6"/>
+    <tableColumn id="27" xr3:uid="{7265A8D0-CFF6-415F-835D-AB8059EE6183}" name="ODP" dataDxfId="5"/>
+    <tableColumn id="28" xr3:uid="{3BF8A3E1-4D9A-459C-B9C8-5CD0C527F418}" name="ASHRAE 34 Safety Classification" dataDxfId="4"/>
+    <tableColumn id="29" xr3:uid="{27A813A0-C128-44A4-AA80-8DA82CC43079}" name="Standard InChI Key" dataDxfId="3"/>
+    <tableColumn id="30" xr3:uid="{CA650C7B-A0BE-4110-8763-174A6A5C98DF}" name="Standard InChI String" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3304,6 +3238,7 @@
   <dimension ref="A1:AO149"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="21.77734375" customWidth="1"/>
     <col min="2" max="2" width="12.21875" customWidth="1"/>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
     <col min="4" max="4" width="10.6640625" customWidth="1"/>
@@ -3330,7 +3265,7 @@
     <col min="31" max="31" width="20.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="67.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:41" ht="54" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -4040,7 +3975,9 @@
       <c r="Z8" s="5">
         <v>0.5</v>
       </c>
-      <c r="AA8" s="5"/>
+      <c r="AA8" s="5">
+        <v>0</v>
+      </c>
       <c r="AB8" s="5"/>
       <c r="AC8" s="5" t="s">
         <v>101</v>
@@ -4123,8 +4060,12 @@
       <c r="Y9" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="Z9" s="5"/>
-      <c r="AA9" s="5"/>
+      <c r="Z9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="5">
+        <v>0</v>
+      </c>
       <c r="AB9" s="5"/>
       <c r="AC9" s="5" t="s">
         <v>113</v>
@@ -4548,7 +4489,9 @@
         <v>173</v>
       </c>
       <c r="Z14" s="5"/>
-      <c r="AA14" s="5"/>
+      <c r="AA14" s="5">
+        <v>0</v>
+      </c>
       <c r="AB14" s="5"/>
       <c r="AC14" s="5" t="s">
         <v>174</v>
@@ -4631,8 +4574,12 @@
       <c r="Y15" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="Z15" s="5"/>
-      <c r="AA15" s="5"/>
+      <c r="Z15" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="5">
+        <v>0</v>
+      </c>
       <c r="AB15" s="5"/>
       <c r="AC15" s="5" t="s">
         <v>181</v>
@@ -6687,74 +6634,74 @@
       <c r="A41" s="17" t="s">
         <v>408</v>
       </c>
-      <c r="B41" s="18"/>
-      <c r="C41" s="18" t="s">
+      <c r="B41" s="5"/>
+      <c r="C41" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="D41" s="18" t="s">
+      <c r="D41" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="E41" s="18" t="s">
+      <c r="E41" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="F41" s="18" t="s">
+      <c r="F41" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="G41" s="18" t="s">
+      <c r="G41" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="H41" s="18">
+      <c r="H41" s="5">
         <v>458.99328000000003</v>
       </c>
-      <c r="I41" s="18">
+      <c r="I41" s="5">
         <v>532.90499999999997</v>
       </c>
-      <c r="J41" s="18">
+      <c r="J41" s="5">
         <v>214.15</v>
       </c>
       <c r="K41" s="2">
         <v>653.20000000000005</v>
       </c>
-      <c r="L41" s="18">
+      <c r="L41" s="5">
         <v>0.84036999999999995</v>
       </c>
-      <c r="M41" s="18">
+      <c r="M41" s="5">
         <v>0.56999999999999995</v>
       </c>
-      <c r="N41" s="18">
+      <c r="N41" s="5">
         <v>1.3080000000000001</v>
       </c>
-      <c r="O41" s="18">
+      <c r="O41" s="5">
         <v>0.80600000000000005</v>
       </c>
-      <c r="P41" s="18"/>
-      <c r="Q41" s="19"/>
-      <c r="R41" s="18" t="s">
+      <c r="P41" s="5"/>
+      <c r="Q41" s="6"/>
+      <c r="R41" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="S41" s="18">
+      <c r="S41" s="5">
         <v>214.15</v>
       </c>
-      <c r="T41" s="18">
+      <c r="T41" s="5">
         <v>655</v>
       </c>
-      <c r="U41" s="18">
+      <c r="U41" s="5">
         <v>125</v>
       </c>
-      <c r="V41" s="18" t="s">
+      <c r="V41" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="W41" s="18" t="s">
+      <c r="W41" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="X41" s="18" t="s">
+      <c r="X41" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="Y41" s="18"/>
-      <c r="Z41" s="18"/>
-      <c r="AA41" s="18"/>
-      <c r="AB41" s="18"/>
-      <c r="AC41" s="18" t="s">
+      <c r="Y41" s="5"/>
+      <c r="Z41" s="5"/>
+      <c r="AA41" s="5"/>
+      <c r="AB41" s="5"/>
+      <c r="AC41" s="5" t="s">
         <v>414</v>
       </c>
       <c r="AD41" s="11" t="s">
@@ -7009,74 +6956,74 @@
       <c r="A45" s="17" t="s">
         <v>445</v>
       </c>
-      <c r="B45" s="18"/>
-      <c r="C45" s="18" t="s">
+      <c r="B45" s="5"/>
+      <c r="C45" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="D45" s="18" t="s">
+      <c r="D45" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="E45" s="18" t="s">
+      <c r="E45" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="F45" s="18" t="s">
+      <c r="F45" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="G45" s="18" t="s">
+      <c r="G45" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="H45" s="18">
+      <c r="H45" s="5">
         <v>294.47206</v>
       </c>
-      <c r="I45" s="18">
+      <c r="I45" s="5">
         <v>628.84</v>
       </c>
-      <c r="J45" s="18">
+      <c r="J45" s="5">
         <v>238.1</v>
       </c>
       <c r="K45" s="2">
         <v>799</v>
       </c>
-      <c r="L45" s="18">
+      <c r="L45" s="5">
         <v>1.341</v>
       </c>
-      <c r="M45" s="18">
+      <c r="M45" s="5">
         <v>0.80840000000000001</v>
       </c>
-      <c r="N45" s="18">
+      <c r="N45" s="5">
         <v>1.79</v>
       </c>
-      <c r="O45" s="18">
+      <c r="O45" s="5">
         <v>0.80500000000000005</v>
       </c>
-      <c r="P45" s="18"/>
-      <c r="Q45" s="19"/>
-      <c r="R45" s="18" t="s">
+      <c r="P45" s="5"/>
+      <c r="Q45" s="6"/>
+      <c r="R45" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="S45" s="18">
+      <c r="S45" s="5">
         <v>238.1</v>
       </c>
-      <c r="T45" s="18">
+      <c r="T45" s="5">
         <v>1000</v>
       </c>
-      <c r="U45" s="18">
+      <c r="U45" s="5">
         <v>50</v>
       </c>
-      <c r="V45" s="18" t="s">
+      <c r="V45" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="W45" s="18" t="s">
+      <c r="W45" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="X45" s="18" t="s">
+      <c r="X45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="Y45" s="18"/>
-      <c r="Z45" s="18"/>
-      <c r="AA45" s="18"/>
-      <c r="AB45" s="18"/>
-      <c r="AC45" s="18" t="s">
+      <c r="Y45" s="5"/>
+      <c r="Z45" s="5"/>
+      <c r="AA45" s="5"/>
+      <c r="AB45" s="5"/>
+      <c r="AC45" s="5" t="s">
         <v>453</v>
       </c>
       <c r="AD45" s="11" t="s">
@@ -9121,8 +9068,12 @@
         <v>103</v>
       </c>
       <c r="Y70" s="5"/>
-      <c r="Z70" s="5"/>
-      <c r="AA70" s="5"/>
+      <c r="Z70" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA70" s="5">
+        <v>0</v>
+      </c>
       <c r="AB70" s="5"/>
       <c r="AC70" s="5" t="s">
         <v>682</v>
@@ -9204,7 +9155,9 @@
       <c r="Z71" s="5">
         <v>2</v>
       </c>
-      <c r="AA71" s="5"/>
+      <c r="AA71" s="5">
+        <v>0</v>
+      </c>
       <c r="AB71" s="5" t="s">
         <v>105</v>
       </c>
@@ -9454,7 +9407,9 @@
       <c r="Z74" s="5">
         <v>726</v>
       </c>
-      <c r="AA74" s="5"/>
+      <c r="AA74" s="5">
+        <v>0</v>
+      </c>
       <c r="AB74" s="5"/>
       <c r="AC74" s="5" t="s">
         <v>722</v>
@@ -9534,7 +9489,9 @@
       <c r="Z75" s="5">
         <v>1030</v>
       </c>
-      <c r="AA75" s="5"/>
+      <c r="AA75" s="5">
+        <v>0</v>
+      </c>
       <c r="AB75" s="5" t="s">
         <v>660</v>
       </c>
@@ -9616,7 +9573,9 @@
       <c r="Z76" s="5">
         <v>794</v>
       </c>
-      <c r="AA76" s="5"/>
+      <c r="AA76" s="5">
+        <v>0</v>
+      </c>
       <c r="AB76" s="5"/>
       <c r="AC76" s="5" t="s">
         <v>741</v>
@@ -9693,8 +9652,12 @@
         <v>103</v>
       </c>
       <c r="Y77" s="5"/>
-      <c r="Z77" s="5"/>
-      <c r="AA77" s="5"/>
+      <c r="Z77" s="5">
+        <v>286</v>
+      </c>
+      <c r="AA77" s="5">
+        <v>0</v>
+      </c>
       <c r="AB77" s="5"/>
       <c r="AC77" s="5" t="s">
         <v>751</v>
@@ -9942,7 +9905,9 @@
       <c r="Z80" s="5">
         <v>2.7</v>
       </c>
-      <c r="AA80" s="5"/>
+      <c r="AA80" s="5">
+        <v>0</v>
+      </c>
       <c r="AB80" s="5"/>
       <c r="AC80" s="5" t="s">
         <v>781</v>
@@ -10205,78 +10170,78 @@
       <c r="A84" s="17" t="s">
         <v>811</v>
       </c>
-      <c r="B84" s="18"/>
-      <c r="C84" s="18" t="s">
+      <c r="B84" s="5"/>
+      <c r="C84" s="5" t="s">
         <v>811</v>
       </c>
-      <c r="D84" s="18" t="s">
+      <c r="D84" s="5" t="s">
         <v>812</v>
       </c>
-      <c r="E84" s="18" t="s">
+      <c r="E84" s="5" t="s">
         <v>813</v>
       </c>
-      <c r="F84" s="18" t="s">
+      <c r="F84" s="5" t="s">
         <v>814</v>
       </c>
-      <c r="G84" s="18" t="s">
+      <c r="G84" s="5" t="s">
         <v>814</v>
       </c>
-      <c r="H84" s="18">
+      <c r="H84" s="5">
         <v>18.015267999999999</v>
       </c>
-      <c r="I84" s="18">
+      <c r="I84" s="5">
         <v>373.12430000000001</v>
       </c>
-      <c r="J84" s="18">
+      <c r="J84" s="5">
         <v>273.16000000000003</v>
       </c>
       <c r="K84" s="2">
         <v>647.096</v>
       </c>
-      <c r="L84" s="18">
+      <c r="L84" s="5">
         <v>22.064</v>
       </c>
-      <c r="M84" s="18">
+      <c r="M84" s="5">
         <v>17.873727995599999</v>
       </c>
-      <c r="N84" s="18">
+      <c r="N84" s="5">
         <v>1.855</v>
       </c>
-      <c r="O84" s="18">
+      <c r="O84" s="5">
         <v>0.34429999999999999</v>
       </c>
-      <c r="P84" s="18">
+      <c r="P84" s="5">
         <v>44.015999999999998</v>
       </c>
-      <c r="Q84" s="19"/>
-      <c r="R84" s="18" t="s">
+      <c r="Q84" s="6"/>
+      <c r="R84" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="S84" s="18">
+      <c r="S84" s="5">
         <v>251.16499999999999</v>
       </c>
-      <c r="T84" s="18">
+      <c r="T84" s="5">
         <v>2000</v>
       </c>
-      <c r="U84" s="18">
+      <c r="U84" s="5">
         <v>1000</v>
       </c>
-      <c r="V84" s="18" t="s">
+      <c r="V84" s="5" t="s">
         <v>815</v>
       </c>
-      <c r="W84" s="18" t="s">
+      <c r="W84" s="5" t="s">
         <v>816</v>
       </c>
-      <c r="X84" s="18" t="s">
+      <c r="X84" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="Y84" s="18"/>
-      <c r="Z84" s="18"/>
-      <c r="AA84" s="18"/>
-      <c r="AB84" s="18" t="s">
+      <c r="Y84" s="5"/>
+      <c r="Z84" s="5"/>
+      <c r="AA84" s="5"/>
+      <c r="AB84" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="AC84" s="18" t="s">
+      <c r="AC84" s="5" t="s">
         <v>817</v>
       </c>
       <c r="AD84" s="11" t="s">
@@ -10541,11 +10506,11 @@
       <c r="AE149" s="9"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="L149 K2:K91">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThan">
+  <conditionalFormatting sqref="K2:K91 L149">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
       <formula>$AN$1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="between">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="between">
       <formula>$AJ$1</formula>
       <formula>$AN$1</formula>
     </cfRule>
